--- a/data/trans_camb/IP11A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,47</t>
+          <t>16,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>19,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,31</t>
+          <t>18,39</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,18</t>
+          <t>0,0; 70,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,99</t>
+          <t>0,0; 76,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,45</t>
+          <t>0,0; 55,5</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,03</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>10,64</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 42,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,54</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,23</t>
+          <t>0,0; 45,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,78</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17,28</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,78</t>
+          <t>11,38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,81; 5,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,82</t>
+          <t>-14,66; 10,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,29</t>
+          <t>-23,0; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 5,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 9,86</t>
+          <t>0,0; 43,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 0,0</t>
+          <t>0,0; 55,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 3,11</t>
+          <t>-10,26; 3,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 22,85</t>
+          <t>-2,53; 21,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 21,77</t>
+          <t>-5,1; 20,85</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-45,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>-0,28%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-45,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-0,28%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-38,57%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>100,35%</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,37</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>-10,11</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-10,11</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>20,66</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-5,37</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-10,11</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,11</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,52; 9,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,61</t>
+          <t>-34,92; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,15; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 9,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 0,0</t>
+          <t>0,0; 58,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 2,53</t>
+          <t>-21,29; 2,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 17,84</t>
+          <t>-14,38; 17,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 0,0</t>
+          <t>-24,85; 0,0</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-53,14%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-53,14%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>12,43</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>4,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,05; 1,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,91; 26,58</t>
+          <t>-7,03; 5,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>-4,56; 19,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 2,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 5,64</t>
+          <t>3,17; 26,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 18,62</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,03</t>
+          <t>-5,21; 1,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 10,34</t>
+          <t>-0,8; 11,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 16,31</t>
+          <t>-1,1; 14,32</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-56,05%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>-20,97%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>73,08%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-56,05%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-20,97%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>-54,55%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>221,88%</t>
+          <t>212,36%</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,23; —</t>
+          <t>-54,82; 1419,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,03; —</t>
         </is>
       </c>
     </row>
